--- a/TestComponents/TestSets/WS1/FieldConfigs.xlsx
+++ b/TestComponents/TestSets/WS1/FieldConfigs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\FieldNBalance\TestComponents\TestSets\WS1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E0555B-EA97-452D-80AF-E7B195AA5DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6585B68E-A7B0-4078-85B6-D078F4044496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{D68C7BAB-80DE-42A0-A5F7-D611BF3989D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D68C7BAB-80DE-42A0-A5F7-D611BF3989D6}"/>
   </bookViews>
   <sheets>
     <sheet name="LincolnRot1" sheetId="3" r:id="rId1"/>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="125">
   <si>
     <t>InitialN</t>
   </si>
@@ -483,6 +483,9 @@
   </si>
   <si>
     <t>Top30cm</t>
+  </si>
+  <si>
+    <t>FinalFertDate</t>
   </si>
 </sst>
 </file>
@@ -1129,21 +1132,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050A90A1-2F9B-4EC2-8DA6-AD1920316E14}">
-  <dimension ref="A1:K54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" customWidth="1"/>
-    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.33203125" customWidth="1"/>
-    <col min="9" max="9" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.28515625" customWidth="1"/>
+    <col min="9" max="9" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="B1" s="14" t="s">
         <v>53</v>
@@ -1174,7 +1177,7 @@
       </c>
       <c r="K1" s="13"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>54</v>
       </c>
@@ -1206,7 +1209,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="34"/>
       <c r="B3" t="s">
         <v>0</v>
@@ -1236,7 +1239,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="34"/>
       <c r="B4" t="s">
         <v>68</v>
@@ -1266,7 +1269,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="34"/>
       <c r="B5" t="s">
         <v>70</v>
@@ -1296,7 +1299,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="34"/>
       <c r="B6" t="s">
         <v>71</v>
@@ -1326,7 +1329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="34"/>
       <c r="B7" t="s">
         <v>1</v>
@@ -1356,7 +1359,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="34"/>
       <c r="B8" t="s">
         <v>2</v>
@@ -1386,7 +1389,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="34"/>
       <c r="B9" t="s">
         <v>3</v>
@@ -1416,7 +1419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="34"/>
       <c r="B10" t="s">
         <v>4</v>
@@ -1446,7 +1449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="34"/>
       <c r="B11" t="s">
         <v>6</v>
@@ -1476,133 +1479,109 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="34"/>
-      <c r="B12" s="13" t="s">
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34"/>
+      <c r="B13" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="13"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>109</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>75</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>77</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>114</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G14" t="s">
         <v>109</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H14" t="s">
         <v>75</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I14" t="s">
         <v>77</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J14" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="25">
-        <v>70</v>
-      </c>
-      <c r="D14" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="E14">
-        <v>16</v>
-      </c>
-      <c r="F14">
-        <v>75</v>
-      </c>
-      <c r="G14" s="25">
-        <v>70</v>
-      </c>
-      <c r="H14" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="I14">
-        <v>16</v>
-      </c>
-      <c r="J14">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="35"/>
       <c r="B15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="C15" s="25">
+        <v>70</v>
+      </c>
+      <c r="D15" s="27">
+        <v>10.3</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="G15" s="25">
+        <v>70</v>
+      </c>
+      <c r="H15" s="27">
+        <v>10.3</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="35"/>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1629,310 +1608,313 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="35"/>
       <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="25">
-        <v>77</v>
+        <v>11</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>87</v>
-      </c>
-      <c r="G17" s="25">
-        <v>77</v>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="35"/>
       <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="26">
-        <v>43753</v>
-      </c>
-      <c r="D18" s="1">
-        <v>43969</v>
-      </c>
-      <c r="E18" s="1">
-        <v>44258</v>
-      </c>
-      <c r="F18" s="1">
-        <v>44446</v>
-      </c>
-      <c r="G18" s="26">
-        <v>43753</v>
-      </c>
-      <c r="H18" s="1">
-        <v>43969</v>
-      </c>
-      <c r="I18" s="1">
-        <v>44258</v>
-      </c>
-      <c r="J18" s="1">
-        <v>44446</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="C18" s="25">
+        <v>77</v>
+      </c>
+      <c r="D18">
+        <v>14</v>
+      </c>
+      <c r="E18">
+        <v>89</v>
+      </c>
+      <c r="F18">
+        <v>87</v>
+      </c>
+      <c r="G18" s="25">
+        <v>77</v>
+      </c>
+      <c r="H18">
+        <v>14</v>
+      </c>
+      <c r="I18">
+        <v>89</v>
+      </c>
+      <c r="J18">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="35"/>
       <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="C19" s="26">
+        <v>43753</v>
+      </c>
+      <c r="D19" s="1">
+        <v>43969</v>
+      </c>
+      <c r="E19" s="1">
+        <v>44258</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44446</v>
+      </c>
+      <c r="G19" s="26">
+        <v>43753</v>
+      </c>
+      <c r="H19" s="1">
+        <v>43969</v>
+      </c>
+      <c r="I19" s="1">
+        <v>44258</v>
+      </c>
+      <c r="J19" s="1">
+        <v>44446</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="35"/>
       <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="26">
-        <v>43905</v>
-      </c>
-      <c r="D20" s="1">
-        <v>44218</v>
-      </c>
-      <c r="E20" s="1">
-        <v>44379</v>
-      </c>
-      <c r="F20" s="1">
-        <v>44623</v>
-      </c>
-      <c r="G20" s="26">
-        <v>43905</v>
-      </c>
-      <c r="H20" s="1">
-        <v>44218</v>
-      </c>
-      <c r="I20" s="1">
-        <v>44379</v>
-      </c>
-      <c r="J20" s="1">
-        <v>44623</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="35"/>
       <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C21" s="26">
+        <v>43905</v>
+      </c>
+      <c r="D21" s="1">
+        <v>44218</v>
+      </c>
+      <c r="E21" s="1">
+        <v>44379</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44623</v>
+      </c>
+      <c r="G21" s="26">
+        <v>43905</v>
+      </c>
+      <c r="H21" s="1">
+        <v>44218</v>
+      </c>
+      <c r="I21" s="1">
+        <v>44379</v>
+      </c>
+      <c r="J21" s="1">
+        <v>44623</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="35"/>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="35"/>
       <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="35"/>
+      <c r="B24" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
+      <c r="C24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>75</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>77</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>114</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F25" t="s">
         <v>103</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G25" t="s">
         <v>75</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H25" t="s">
         <v>77</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I25" t="s">
         <v>114</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J25" t="s">
         <v>103</v>
       </c>
-      <c r="K24" s="12"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="D25">
-        <v>16</v>
-      </c>
-      <c r="E25">
-        <v>75</v>
-      </c>
-      <c r="F25">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G25" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="H25">
-        <v>16</v>
-      </c>
-      <c r="I25">
-        <v>75</v>
-      </c>
-      <c r="J25">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="37"/>
       <c r="B26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
+        <v>73</v>
+      </c>
+      <c r="C26" s="27">
+        <v>10.3</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G26" s="27">
+        <v>10.3</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="J26">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="37"/>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1956,310 +1938,310 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="37"/>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>87</v>
-      </c>
-      <c r="J28">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="37"/>
       <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="1">
-        <v>43969</v>
-      </c>
-      <c r="D29" s="1">
-        <v>44258</v>
-      </c>
-      <c r="E29" s="1">
-        <v>44446</v>
-      </c>
-      <c r="F29" s="1">
-        <v>44687</v>
-      </c>
-      <c r="G29" s="1">
-        <v>43969</v>
-      </c>
-      <c r="H29" s="1">
-        <v>44258</v>
-      </c>
-      <c r="I29" s="1">
-        <v>44446</v>
-      </c>
-      <c r="J29" s="1">
-        <v>44687</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>14</v>
+      </c>
+      <c r="D29">
+        <v>89</v>
+      </c>
+      <c r="E29">
+        <v>87</v>
+      </c>
+      <c r="F29">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>14</v>
+      </c>
+      <c r="H29">
+        <v>89</v>
+      </c>
+      <c r="I29">
+        <v>87</v>
+      </c>
+      <c r="J29">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="37"/>
       <c r="B30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
-        <v>51</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="C30" s="1">
+        <v>43969</v>
+      </c>
+      <c r="D30" s="1">
+        <v>44258</v>
+      </c>
+      <c r="E30" s="1">
+        <v>44446</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44687</v>
+      </c>
+      <c r="G30" s="1">
+        <v>43969</v>
+      </c>
+      <c r="H30" s="1">
+        <v>44258</v>
+      </c>
+      <c r="I30" s="1">
+        <v>44446</v>
+      </c>
+      <c r="J30" s="1">
+        <v>44687</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="37"/>
       <c r="B31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="1">
-        <v>44218</v>
-      </c>
-      <c r="D31" s="1">
-        <v>44379</v>
-      </c>
-      <c r="E31" s="1">
-        <v>44623</v>
-      </c>
-      <c r="F31" s="1">
-        <v>44933</v>
-      </c>
-      <c r="G31" s="1">
-        <v>44218</v>
-      </c>
-      <c r="H31" s="1">
-        <v>44379</v>
-      </c>
-      <c r="I31" s="1">
-        <v>44623</v>
-      </c>
-      <c r="J31" s="1">
-        <v>44933</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="37"/>
       <c r="B32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" t="s">
-        <v>49</v>
-      </c>
-      <c r="F32" t="s">
-        <v>49</v>
-      </c>
-      <c r="G32" t="s">
-        <v>49</v>
-      </c>
-      <c r="H32" t="s">
-        <v>18</v>
-      </c>
-      <c r="I32" t="s">
-        <v>49</v>
-      </c>
-      <c r="J32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="C32" s="1">
+        <v>44218</v>
+      </c>
+      <c r="D32" s="1">
+        <v>44379</v>
+      </c>
+      <c r="E32" s="1">
+        <v>44623</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44933</v>
+      </c>
+      <c r="G32" s="1">
+        <v>44218</v>
+      </c>
+      <c r="H32" s="1">
+        <v>44379</v>
+      </c>
+      <c r="I32" s="1">
+        <v>44623</v>
+      </c>
+      <c r="J32" s="1">
+        <v>44933</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="37"/>
       <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" t="s">
+        <v>49</v>
+      </c>
+      <c r="J33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" t="s">
         <v>32</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>52</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>20</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E34" t="s">
         <v>20</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>52</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G34" t="s">
         <v>52</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H34" t="s">
         <v>20</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I34" t="s">
         <v>20</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="38"/>
-      <c r="B34" s="13" t="s">
+    <row r="35" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="38"/>
+      <c r="B35" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K34" s="13"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="35" t="s">
+      <c r="C35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="13"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>34</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>77</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>114</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E36" t="s">
         <v>103</v>
       </c>
-      <c r="F35" s="31" t="s">
+      <c r="F36" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G36" t="s">
         <v>77</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H36" t="s">
         <v>114</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I36" t="s">
         <v>103</v>
       </c>
-      <c r="J35" s="31" t="s">
+      <c r="J36" s="31" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="35"/>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36">
-        <v>16</v>
-      </c>
-      <c r="D36">
-        <v>75</v>
-      </c>
-      <c r="E36">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F36" s="31">
-        <v>3</v>
-      </c>
-      <c r="G36">
-        <v>16</v>
-      </c>
-      <c r="H36">
-        <v>75</v>
-      </c>
-      <c r="I36">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J36" s="31">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="35"/>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F37" s="31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="I37">
+        <v>2.2999999999999998</v>
       </c>
       <c r="J37" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="35"/>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2283,249 +2265,262 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="35"/>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F39" s="31">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>87</v>
-      </c>
-      <c r="I39">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J39" s="31">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="35"/>
       <c r="B40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="1">
-        <v>44258</v>
-      </c>
-      <c r="D40" s="1">
-        <v>44446</v>
-      </c>
-      <c r="E40" s="1">
-        <v>44687</v>
-      </c>
-      <c r="F40" s="32">
-        <v>44986</v>
-      </c>
-      <c r="G40" s="1">
-        <v>44258</v>
-      </c>
-      <c r="H40" s="1">
-        <v>44446</v>
-      </c>
-      <c r="I40" s="1">
-        <v>44687</v>
-      </c>
-      <c r="J40" s="32">
-        <v>44986</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="C40">
+        <v>89</v>
+      </c>
+      <c r="D40">
+        <v>87</v>
+      </c>
+      <c r="E40">
+        <v>14</v>
+      </c>
+      <c r="F40" s="31">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>89</v>
+      </c>
+      <c r="H40">
+        <v>87</v>
+      </c>
+      <c r="I40">
+        <v>14</v>
+      </c>
+      <c r="J40" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="35"/>
       <c r="B41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" t="s">
-        <v>51</v>
-      </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" t="s">
-        <v>51</v>
-      </c>
-      <c r="H41" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" s="31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="C41" s="1">
+        <v>44258</v>
+      </c>
+      <c r="D41" s="1">
+        <v>44446</v>
+      </c>
+      <c r="E41" s="1">
+        <v>44687</v>
+      </c>
+      <c r="F41" s="32">
+        <v>44986</v>
+      </c>
+      <c r="G41" s="1">
+        <v>44258</v>
+      </c>
+      <c r="H41" s="1">
+        <v>44446</v>
+      </c>
+      <c r="I41" s="1">
+        <v>44687</v>
+      </c>
+      <c r="J41" s="32">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="35"/>
       <c r="B42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="1">
-        <v>44379</v>
-      </c>
-      <c r="D42" s="1">
-        <v>44623</v>
-      </c>
-      <c r="E42" s="1">
-        <v>44933</v>
-      </c>
-      <c r="F42" s="32">
-        <v>45072</v>
-      </c>
-      <c r="G42" s="1">
-        <v>44379</v>
-      </c>
-      <c r="H42" s="1">
-        <v>44623</v>
-      </c>
-      <c r="I42" s="1">
-        <v>44933</v>
-      </c>
-      <c r="J42" s="32">
-        <v>45072</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s">
+        <v>51</v>
+      </c>
+      <c r="H42" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="35"/>
       <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E43" t="s">
-        <v>49</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" t="s">
-        <v>18</v>
-      </c>
-      <c r="H43" t="s">
-        <v>49</v>
-      </c>
-      <c r="I43" t="s">
-        <v>49</v>
-      </c>
-      <c r="J43" s="31" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="C43" s="1">
+        <v>44379</v>
+      </c>
+      <c r="D43" s="1">
+        <v>44623</v>
+      </c>
+      <c r="E43" s="1">
+        <v>44933</v>
+      </c>
+      <c r="F43" s="32">
+        <v>45072</v>
+      </c>
+      <c r="G43" s="1">
+        <v>44379</v>
+      </c>
+      <c r="H43" s="1">
+        <v>44623</v>
+      </c>
+      <c r="I43" s="1">
+        <v>44933</v>
+      </c>
+      <c r="J43" s="32">
+        <v>45072</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="35"/>
       <c r="B44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" t="s">
+        <v>49</v>
+      </c>
+      <c r="J44" s="31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="35"/>
+      <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>20</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>20</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E45" t="s">
         <v>52</v>
       </c>
-      <c r="F44" s="31" t="s">
+      <c r="F45" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G45" t="s">
         <v>20</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H45" t="s">
         <v>20</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I45" t="s">
         <v>52</v>
       </c>
-      <c r="J44" s="31" t="s">
+      <c r="J45" s="31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="35"/>
-      <c r="B45" s="13" t="s">
+    <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="35"/>
+      <c r="B46" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F45" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="K45" s="13"/>
-    </row>
-    <row r="49" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B50" s="9" t="s">
+      <c r="C46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="13"/>
+    </row>
+    <row r="50" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B51" s="4" t="s">
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="3"/>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B52" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="6"/>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B52" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
@@ -2537,9 +2532,9 @@
       <c r="J52" s="5"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -2551,26 +2546,40 @@
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="11" t="s">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="6"/>
+    </row>
+    <row r="55" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="8"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="A14:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -2579,18 +2588,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5455F7E-3498-453E-982D-C120B5675E13}">
-  <dimension ref="A1:P55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
-    <col min="5" max="7" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37" customWidth="1"/>
-    <col min="9" max="10" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="B1" s="14" t="s">
         <v>53</v>
@@ -2626,7 +2635,7 @@
       <c r="O1" s="13"/>
       <c r="P1" s="13"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>54</v>
       </c>
@@ -2658,7 +2667,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="34"/>
       <c r="B3" t="s">
         <v>0</v>
@@ -2688,7 +2697,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="34"/>
       <c r="B4" t="s">
         <v>68</v>
@@ -2718,7 +2727,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="34"/>
       <c r="B5" t="s">
         <v>70</v>
@@ -2748,7 +2757,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="34"/>
       <c r="B6" t="s">
         <v>71</v>
@@ -2778,7 +2787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="34"/>
       <c r="B7" t="s">
         <v>1</v>
@@ -2808,7 +2817,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="34"/>
       <c r="B8" t="s">
         <v>2</v>
@@ -2838,7 +2847,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="34"/>
       <c r="B9" t="s">
         <v>3</v>
@@ -2868,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="34"/>
       <c r="B10" t="s">
         <v>4</v>
@@ -2898,7 +2907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="34"/>
       <c r="B11" t="s">
         <v>6</v>
@@ -2928,138 +2937,114 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="34"/>
-      <c r="B12" s="13" t="s">
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34"/>
+      <c r="B13" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C14" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>83</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>35</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>110</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G14" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H14" t="s">
         <v>83</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I14" t="s">
         <v>35</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="31">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>59</v>
-      </c>
-      <c r="E14">
-        <v>7.5</v>
-      </c>
-      <c r="F14">
-        <v>92</v>
-      </c>
-      <c r="G14" s="31">
-        <v>3</v>
-      </c>
-      <c r="H14">
-        <v>59</v>
-      </c>
-      <c r="I14">
-        <v>7.5</v>
-      </c>
-      <c r="J14">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="35"/>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="C15" s="31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G15" s="31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="35"/>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="31">
         <v>0</v>
@@ -3086,318 +3071,318 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="35"/>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="31">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G17" s="31">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="35"/>
       <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="32">
-        <v>43891</v>
-      </c>
-      <c r="D18" s="1">
-        <v>44172</v>
-      </c>
-      <c r="E18" s="1">
-        <v>44257</v>
-      </c>
-      <c r="F18" s="1">
-        <v>44491</v>
-      </c>
-      <c r="G18" s="32">
-        <v>43891</v>
-      </c>
-      <c r="H18" s="1">
-        <v>44172</v>
-      </c>
-      <c r="I18" s="1">
-        <v>44257</v>
-      </c>
-      <c r="J18" s="1">
-        <v>44491</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="C18" s="31">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>94</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>75</v>
+      </c>
+      <c r="G18" s="31">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>94</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="35"/>
       <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="C19" s="32">
+        <v>43891</v>
+      </c>
+      <c r="D19" s="1">
+        <v>44172</v>
+      </c>
+      <c r="E19" s="1">
+        <v>44257</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44491</v>
+      </c>
+      <c r="G19" s="32">
+        <v>43891</v>
+      </c>
+      <c r="H19" s="1">
+        <v>44172</v>
+      </c>
+      <c r="I19" s="1">
+        <v>44257</v>
+      </c>
+      <c r="J19" s="1">
+        <v>44491</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="35"/>
       <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="32">
-        <v>44105</v>
-      </c>
-      <c r="D20" s="1">
-        <v>44219</v>
-      </c>
-      <c r="E20" s="1">
-        <v>44407</v>
-      </c>
-      <c r="F20" s="17">
-        <v>44629</v>
-      </c>
-      <c r="G20" s="32">
-        <v>44105</v>
-      </c>
-      <c r="H20" s="1">
-        <v>44219</v>
-      </c>
-      <c r="I20" s="1">
-        <v>44407</v>
-      </c>
-      <c r="J20" s="17">
-        <v>44629</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="35"/>
       <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" t="s">
-        <v>84</v>
-      </c>
-      <c r="J21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C21" s="32">
+        <v>44105</v>
+      </c>
+      <c r="D21" s="1">
+        <v>44219</v>
+      </c>
+      <c r="E21" s="1">
+        <v>44407</v>
+      </c>
+      <c r="F21" s="17">
+        <v>44629</v>
+      </c>
+      <c r="G21" s="32">
+        <v>44105</v>
+      </c>
+      <c r="H21" s="1">
+        <v>44219</v>
+      </c>
+      <c r="I21" s="1">
+        <v>44407</v>
+      </c>
+      <c r="J21" s="17">
+        <v>44629</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="35"/>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="35"/>
       <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="35"/>
+      <c r="B24" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
+      <c r="C24" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>83</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>35</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>110</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F25" t="s">
         <v>103</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G25" t="s">
         <v>83</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H25" t="s">
         <v>35</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I25" t="s">
         <v>110</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J25" t="s">
         <v>103</v>
       </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25">
-        <v>59</v>
-      </c>
-      <c r="D25">
-        <v>7.5</v>
-      </c>
-      <c r="E25">
-        <v>92</v>
-      </c>
-      <c r="F25">
-        <v>1.51</v>
-      </c>
-      <c r="G25">
-        <v>59</v>
-      </c>
-      <c r="H25">
-        <v>7.5</v>
-      </c>
-      <c r="I25">
-        <v>92</v>
-      </c>
-      <c r="J25">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="37"/>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="37"/>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3424,318 +3409,318 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="37"/>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="37"/>
       <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="1">
-        <v>44172</v>
-      </c>
-      <c r="D29" s="1">
-        <v>44257</v>
-      </c>
-      <c r="E29" s="1">
-        <v>44491</v>
-      </c>
-      <c r="F29" s="1">
-        <v>44691</v>
-      </c>
-      <c r="G29" s="1">
-        <v>44172</v>
-      </c>
-      <c r="H29" s="1">
-        <v>44257</v>
-      </c>
-      <c r="I29" s="1">
-        <v>44491</v>
-      </c>
-      <c r="J29" s="1">
-        <v>44691</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>94</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>75</v>
+      </c>
+      <c r="F29">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>94</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>75</v>
+      </c>
+      <c r="J29">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="37"/>
       <c r="B30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="C30" s="1">
+        <v>44172</v>
+      </c>
+      <c r="D30" s="1">
+        <v>44257</v>
+      </c>
+      <c r="E30" s="1">
+        <v>44491</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44691</v>
+      </c>
+      <c r="G30" s="1">
+        <v>44172</v>
+      </c>
+      <c r="H30" s="1">
+        <v>44257</v>
+      </c>
+      <c r="I30" s="1">
+        <v>44491</v>
+      </c>
+      <c r="J30" s="1">
+        <v>44691</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="37"/>
       <c r="B31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="1">
-        <v>44219</v>
-      </c>
-      <c r="D31" s="1">
-        <v>44407</v>
-      </c>
-      <c r="E31" s="17">
-        <v>44629</v>
-      </c>
-      <c r="F31" s="17">
-        <v>44933</v>
-      </c>
-      <c r="G31" s="1">
-        <v>44219</v>
-      </c>
-      <c r="H31" s="1">
-        <v>44407</v>
-      </c>
-      <c r="I31" s="17">
-        <v>44629</v>
-      </c>
-      <c r="J31" s="17">
-        <v>44933</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="37"/>
       <c r="B32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" t="s">
-        <v>49</v>
-      </c>
-      <c r="F32" t="s">
-        <v>49</v>
-      </c>
-      <c r="G32" t="s">
-        <v>62</v>
-      </c>
-      <c r="H32" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32" t="s">
-        <v>49</v>
-      </c>
-      <c r="J32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="C32" s="1">
+        <v>44219</v>
+      </c>
+      <c r="D32" s="1">
+        <v>44407</v>
+      </c>
+      <c r="E32" s="17">
+        <v>44629</v>
+      </c>
+      <c r="F32" s="17">
+        <v>44933</v>
+      </c>
+      <c r="G32" s="1">
+        <v>44219</v>
+      </c>
+      <c r="H32" s="1">
+        <v>44407</v>
+      </c>
+      <c r="I32" s="17">
+        <v>44629</v>
+      </c>
+      <c r="J32" s="17">
+        <v>44933</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="37"/>
       <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33" t="s">
+        <v>49</v>
+      </c>
+      <c r="J33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" t="s">
         <v>32</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>20</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>20</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E34" t="s">
         <v>20</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>52</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G34" t="s">
         <v>20</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H34" t="s">
         <v>20</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I34" t="s">
         <v>20</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="38"/>
-      <c r="B34" s="13" t="s">
+    <row r="35" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="38"/>
+      <c r="B35" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="13"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="35" t="s">
+      <c r="C35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>34</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>35</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>110</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E36" t="s">
         <v>103</v>
       </c>
-      <c r="F35" s="31" t="s">
+      <c r="F36" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G36" t="s">
         <v>35</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H36" t="s">
         <v>110</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I36" t="s">
         <v>103</v>
       </c>
-      <c r="J35" s="31" t="s">
+      <c r="J36" s="31" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="35"/>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36">
-        <v>7.5</v>
-      </c>
-      <c r="D36">
-        <v>92</v>
-      </c>
-      <c r="E36">
-        <v>1.51</v>
-      </c>
-      <c r="F36" s="31">
-        <v>3</v>
-      </c>
-      <c r="G36">
-        <v>7.5</v>
-      </c>
-      <c r="H36">
-        <v>92</v>
-      </c>
-      <c r="I36">
-        <v>1.51</v>
-      </c>
-      <c r="J36" s="31">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="35"/>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="F37" s="31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="J37" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="35"/>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -3762,19 +3747,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="35"/>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F39" s="31">
         <v>0</v>
@@ -3783,249 +3768,260 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J39" s="31">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="35"/>
       <c r="B40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="1">
-        <v>44257</v>
-      </c>
-      <c r="D40" s="1">
-        <v>44491</v>
-      </c>
-      <c r="E40" s="1">
-        <v>44691</v>
-      </c>
-      <c r="F40" s="32">
-        <v>44986</v>
-      </c>
-      <c r="G40" s="1">
-        <v>44257</v>
-      </c>
-      <c r="H40" s="1">
-        <v>44491</v>
-      </c>
-      <c r="I40" s="1">
-        <v>44691</v>
-      </c>
-      <c r="J40" s="32">
-        <v>44986</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>80</v>
+      </c>
+      <c r="E40">
+        <v>14</v>
+      </c>
+      <c r="F40" s="31">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>80</v>
+      </c>
+      <c r="I40">
+        <v>14</v>
+      </c>
+      <c r="J40" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="35"/>
       <c r="B41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" s="31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="C41" s="1">
+        <v>44257</v>
+      </c>
+      <c r="D41" s="1">
+        <v>44491</v>
+      </c>
+      <c r="E41" s="1">
+        <v>44691</v>
+      </c>
+      <c r="F41" s="32">
+        <v>44986</v>
+      </c>
+      <c r="G41" s="1">
+        <v>44257</v>
+      </c>
+      <c r="H41" s="1">
+        <v>44491</v>
+      </c>
+      <c r="I41" s="1">
+        <v>44691</v>
+      </c>
+      <c r="J41" s="32">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="35"/>
       <c r="B42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="1">
-        <v>44407</v>
-      </c>
-      <c r="D42" s="17">
-        <v>44629</v>
-      </c>
-      <c r="E42" s="17">
-        <v>44933</v>
-      </c>
-      <c r="F42" s="32">
-        <v>45072</v>
-      </c>
-      <c r="G42" s="1">
-        <v>44407</v>
-      </c>
-      <c r="H42" s="17">
-        <v>44629</v>
-      </c>
-      <c r="I42" s="17">
-        <v>44933</v>
-      </c>
-      <c r="J42" s="32">
-        <v>45072</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="35"/>
       <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" t="s">
-        <v>84</v>
-      </c>
-      <c r="D43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E43" t="s">
-        <v>49</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" t="s">
-        <v>84</v>
-      </c>
-      <c r="H43" t="s">
-        <v>49</v>
-      </c>
-      <c r="I43" t="s">
-        <v>49</v>
-      </c>
-      <c r="J43" s="31" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="C43" s="1">
+        <v>44407</v>
+      </c>
+      <c r="D43" s="17">
+        <v>44629</v>
+      </c>
+      <c r="E43" s="17">
+        <v>44933</v>
+      </c>
+      <c r="F43" s="32">
+        <v>45072</v>
+      </c>
+      <c r="G43" s="1">
+        <v>44407</v>
+      </c>
+      <c r="H43" s="17">
+        <v>44629</v>
+      </c>
+      <c r="I43" s="17">
+        <v>44933</v>
+      </c>
+      <c r="J43" s="32">
+        <v>45072</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="35"/>
       <c r="B44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>84</v>
+      </c>
+      <c r="H44" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" t="s">
+        <v>49</v>
+      </c>
+      <c r="J44" s="31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="35"/>
+      <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>20</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>20</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E45" t="s">
         <v>52</v>
       </c>
-      <c r="F44" s="31" t="s">
+      <c r="F45" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G45" t="s">
         <v>20</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H45" t="s">
         <v>20</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I45" t="s">
         <v>52</v>
       </c>
-      <c r="J44" s="31" t="s">
+      <c r="J45" s="31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="35"/>
-      <c r="B45" s="13" t="s">
+    <row r="46" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="35"/>
+      <c r="B46" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F45" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-    </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B50" s="9" t="s">
+      <c r="C46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="13"/>
+    </row>
+    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B51" s="4" t="s">
+      <c r="C51" s="10"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B52" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="6"/>
-    </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B52" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52" s="5"/>
+      <c r="C52" s="24"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
+      <c r="G52" s="24"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
@@ -4036,9 +4032,9 @@
       <c r="O52" s="5"/>
       <c r="P52" s="6"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -4055,9 +4051,9 @@
       <c r="O53" s="5"/>
       <c r="P53" s="6"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -4074,29 +4070,48 @@
       <c r="O54" s="5"/>
       <c r="P54" s="6"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="11"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
-      <c r="P55" s="8"/>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B55" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="6"/>
+    </row>
+    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="11"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="A14:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -4105,18 +4120,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AD42EA-A0EE-4986-A449-DEBA14E52DE4}">
-  <dimension ref="A1:R54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="37" style="15" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" style="15" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="37" style="15" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="B1" s="14" t="s">
         <v>53</v>
@@ -4154,7 +4169,7 @@
       <c r="Q1" s="13"/>
       <c r="R1" s="13"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>54</v>
       </c>
@@ -4186,7 +4201,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="34"/>
       <c r="B3" t="s">
         <v>0</v>
@@ -4216,7 +4231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="34"/>
       <c r="B4" t="s">
         <v>68</v>
@@ -4246,7 +4261,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="34"/>
       <c r="B5" t="s">
         <v>70</v>
@@ -4276,7 +4291,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="34"/>
       <c r="B6" t="s">
         <v>71</v>
@@ -4306,7 +4321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="34"/>
       <c r="B7" t="s">
         <v>1</v>
@@ -4336,7 +4351,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="34"/>
       <c r="B8" t="s">
         <v>2</v>
@@ -4366,7 +4381,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="34"/>
       <c r="B9" t="s">
         <v>3</v>
@@ -4396,7 +4411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="34"/>
       <c r="B10" t="s">
         <v>4</v>
@@ -4426,7 +4441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="34"/>
       <c r="B11" t="s">
         <v>6</v>
@@ -4456,140 +4471,124 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="34"/>
-      <c r="B12" s="13" t="s">
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34"/>
+      <c r="B13" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G13" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H13" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I13" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J13" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C14" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E14" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F14" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G14" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H14" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I14" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J14" s="16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="31">
-        <v>3</v>
-      </c>
-      <c r="D14" s="16">
-        <v>44</v>
-      </c>
-      <c r="E14" s="16">
-        <v>3</v>
-      </c>
-      <c r="F14" s="16">
-        <v>4</v>
-      </c>
-      <c r="G14" s="31">
-        <v>3</v>
-      </c>
-      <c r="H14" s="16">
-        <v>44</v>
-      </c>
-      <c r="I14" s="16">
-        <v>3</v>
-      </c>
-      <c r="J14" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="35"/>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="C15" s="31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" s="16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E15" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" s="31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" s="16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I15" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="35"/>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="31">
         <v>0</v>
@@ -4616,16 +4615,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="35"/>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="31">
         <v>0</v>
       </c>
       <c r="D17" s="16">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="E17" s="16">
         <v>0</v>
@@ -4637,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="16">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="I17" s="16">
         <v>0</v>
@@ -4646,290 +4645,290 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="35"/>
       <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="32">
-        <v>44256</v>
-      </c>
-      <c r="D18" s="17">
-        <v>44464</v>
-      </c>
-      <c r="E18" s="17">
-        <v>44640</v>
-      </c>
-      <c r="F18" s="17">
-        <v>44811</v>
-      </c>
-      <c r="G18" s="32">
-        <v>44256</v>
-      </c>
-      <c r="H18" s="17">
-        <v>44464</v>
-      </c>
-      <c r="I18" s="17">
-        <v>44640</v>
-      </c>
-      <c r="J18" s="17">
-        <v>44811</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="C18" s="31">
+        <v>0</v>
+      </c>
+      <c r="D18" s="16">
+        <v>87</v>
+      </c>
+      <c r="E18" s="16">
+        <v>0</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0</v>
+      </c>
+      <c r="G18" s="31">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <v>87</v>
+      </c>
+      <c r="I18" s="16">
+        <v>0</v>
+      </c>
+      <c r="J18" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="35"/>
       <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="C19" s="32">
+        <v>44256</v>
+      </c>
+      <c r="D19" s="17">
+        <v>44464</v>
+      </c>
+      <c r="E19" s="17">
+        <v>44640</v>
+      </c>
+      <c r="F19" s="17">
+        <v>44811</v>
+      </c>
+      <c r="G19" s="32">
+        <v>44256</v>
+      </c>
+      <c r="H19" s="17">
+        <v>44464</v>
+      </c>
+      <c r="I19" s="17">
+        <v>44640</v>
+      </c>
+      <c r="J19" s="17">
+        <v>44811</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="35"/>
       <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="32">
-        <v>44409</v>
-      </c>
-      <c r="D20" s="17">
-        <v>44602</v>
-      </c>
-      <c r="E20" s="17">
-        <v>44810</v>
-      </c>
-      <c r="F20" s="17">
-        <v>44862</v>
-      </c>
-      <c r="G20" s="32">
-        <v>44409</v>
-      </c>
-      <c r="H20" s="17">
-        <v>44602</v>
-      </c>
-      <c r="I20" s="17">
-        <v>44810</v>
-      </c>
-      <c r="J20" s="17">
-        <v>44862</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="35"/>
       <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C21" s="32">
+        <v>44409</v>
+      </c>
+      <c r="D21" s="17">
+        <v>44602</v>
+      </c>
+      <c r="E21" s="17">
+        <v>44810</v>
+      </c>
+      <c r="F21" s="17">
+        <v>44862</v>
+      </c>
+      <c r="G21" s="32">
+        <v>44409</v>
+      </c>
+      <c r="H21" s="17">
+        <v>44602</v>
+      </c>
+      <c r="I21" s="17">
+        <v>44810</v>
+      </c>
+      <c r="J21" s="17">
+        <v>44862</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="35"/>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="35"/>
       <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="35"/>
+      <c r="B24" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="23" t="s">
+      <c r="C24" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F24" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="G23" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="23" t="s">
+      <c r="G24" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="J24" s="23" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D25" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E25" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F25" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G25" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="16" t="s">
+      <c r="H25" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="I24" s="16" t="s">
+      <c r="I25" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="J24" s="16" t="s">
+      <c r="J25" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="16">
-        <v>44</v>
-      </c>
-      <c r="D25" s="16">
-        <v>3</v>
-      </c>
-      <c r="E25" s="16">
-        <v>4</v>
-      </c>
-      <c r="F25" s="16">
-        <v>4</v>
-      </c>
-      <c r="G25" s="16">
-        <v>44</v>
-      </c>
-      <c r="H25" s="16">
-        <v>3</v>
-      </c>
-      <c r="I25" s="16">
-        <v>4</v>
-      </c>
-      <c r="J25" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="37"/>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C26" s="16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D26" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E26" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F26" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G26" s="16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H26" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J26" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="37"/>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27" s="16">
         <v>0</v>
@@ -4956,13 +4955,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="37"/>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28" s="16">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="D28" s="16">
         <v>0</v>
@@ -4974,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="16">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H28" s="16">
         <v>0</v>
@@ -4986,290 +4985,290 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="37"/>
       <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="17">
-        <v>44464</v>
-      </c>
-      <c r="D29" s="17">
-        <v>44640</v>
-      </c>
-      <c r="E29" s="17">
-        <v>44811</v>
-      </c>
-      <c r="F29" s="17">
-        <v>44863</v>
-      </c>
-      <c r="G29" s="17">
-        <v>44464</v>
-      </c>
-      <c r="H29" s="17">
-        <v>44640</v>
-      </c>
-      <c r="I29" s="17">
-        <v>44811</v>
-      </c>
-      <c r="J29" s="17">
-        <v>44863</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="C29" s="16">
+        <v>87</v>
+      </c>
+      <c r="D29" s="16">
+        <v>0</v>
+      </c>
+      <c r="E29" s="16">
+        <v>0</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0</v>
+      </c>
+      <c r="G29" s="16">
+        <v>87</v>
+      </c>
+      <c r="H29" s="16">
+        <v>0</v>
+      </c>
+      <c r="I29" s="16">
+        <v>0</v>
+      </c>
+      <c r="J29" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="37"/>
       <c r="B30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="C30" s="17">
+        <v>44464</v>
+      </c>
+      <c r="D30" s="17">
+        <v>44640</v>
+      </c>
+      <c r="E30" s="17">
+        <v>44811</v>
+      </c>
+      <c r="F30" s="17">
+        <v>44863</v>
+      </c>
+      <c r="G30" s="17">
+        <v>44464</v>
+      </c>
+      <c r="H30" s="17">
+        <v>44640</v>
+      </c>
+      <c r="I30" s="17">
+        <v>44811</v>
+      </c>
+      <c r="J30" s="17">
+        <v>44863</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="37"/>
       <c r="B31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="17">
-        <v>44602</v>
-      </c>
-      <c r="D31" s="17">
-        <v>44810</v>
-      </c>
-      <c r="E31" s="17">
-        <v>44862</v>
-      </c>
-      <c r="F31" s="17">
-        <v>44895</v>
-      </c>
-      <c r="G31" s="17">
-        <v>44602</v>
-      </c>
-      <c r="H31" s="17">
-        <v>44810</v>
-      </c>
-      <c r="I31" s="17">
-        <v>44862</v>
-      </c>
-      <c r="J31" s="17">
-        <v>44895</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="37"/>
       <c r="B32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="C32" s="17">
+        <v>44602</v>
+      </c>
+      <c r="D32" s="17">
+        <v>44810</v>
+      </c>
+      <c r="E32" s="17">
+        <v>44862</v>
+      </c>
+      <c r="F32" s="17">
+        <v>44895</v>
+      </c>
+      <c r="G32" s="17">
+        <v>44602</v>
+      </c>
+      <c r="H32" s="17">
+        <v>44810</v>
+      </c>
+      <c r="I32" s="17">
+        <v>44862</v>
+      </c>
+      <c r="J32" s="17">
+        <v>44895</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="37"/>
       <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" t="s">
         <v>32</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E34" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F34" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G34" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H34" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I34" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="J33" s="16" t="s">
+      <c r="J34" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="38"/>
-      <c r="B34" s="13" t="s">
+    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="38"/>
+      <c r="B35" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="23" t="s">
+      <c r="C35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E35" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="23" t="s">
+      <c r="F35" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="G34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="23" t="s">
+      <c r="G35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="I34" s="23" t="s">
+      <c r="I35" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J34" s="23" t="s">
+      <c r="J35" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" s="35" t="s">
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C36" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D36" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E36" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="F35" s="31" t="s">
+      <c r="F36" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G36" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H36" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I36" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="J35" s="31" t="s">
+      <c r="J36" s="31" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" s="35"/>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="16">
-        <v>1</v>
-      </c>
-      <c r="D36" s="16">
-        <v>4</v>
-      </c>
-      <c r="E36" s="16">
-        <v>4</v>
-      </c>
-      <c r="F36" s="31">
-        <v>3</v>
-      </c>
-      <c r="G36" s="16">
-        <v>1</v>
-      </c>
-      <c r="H36" s="16">
-        <v>4</v>
-      </c>
-      <c r="I36" s="16">
-        <v>4</v>
-      </c>
-      <c r="J36" s="31">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="35"/>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C37" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E37" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F37" s="31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I37" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J37" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="35"/>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="16">
         <v>0</v>
@@ -5296,13 +5295,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="35"/>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39" s="16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D39" s="16">
         <v>0</v>
@@ -5314,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H39" s="16">
         <v>0</v>
@@ -5326,240 +5325,249 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="35"/>
       <c r="B40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="17">
-        <v>44640</v>
-      </c>
-      <c r="D40" s="17">
-        <v>44811</v>
-      </c>
-      <c r="E40" s="17">
-        <v>44863</v>
-      </c>
-      <c r="F40" s="32">
-        <v>44986</v>
-      </c>
-      <c r="G40" s="17">
-        <v>44640</v>
-      </c>
-      <c r="H40" s="17">
-        <v>44811</v>
-      </c>
-      <c r="I40" s="17">
-        <v>44863</v>
-      </c>
-      <c r="J40" s="32">
-        <v>44986</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="C40" s="16">
+        <v>14</v>
+      </c>
+      <c r="D40" s="16">
+        <v>0</v>
+      </c>
+      <c r="E40" s="16">
+        <v>0</v>
+      </c>
+      <c r="F40" s="31">
+        <v>0</v>
+      </c>
+      <c r="G40" s="16">
+        <v>14</v>
+      </c>
+      <c r="H40" s="16">
+        <v>0</v>
+      </c>
+      <c r="I40" s="16">
+        <v>0</v>
+      </c>
+      <c r="J40" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="35"/>
       <c r="B41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I41" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="J41" s="31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="C41" s="17">
+        <v>44640</v>
+      </c>
+      <c r="D41" s="17">
+        <v>44811</v>
+      </c>
+      <c r="E41" s="17">
+        <v>44863</v>
+      </c>
+      <c r="F41" s="32">
+        <v>44986</v>
+      </c>
+      <c r="G41" s="17">
+        <v>44640</v>
+      </c>
+      <c r="H41" s="17">
+        <v>44811</v>
+      </c>
+      <c r="I41" s="17">
+        <v>44863</v>
+      </c>
+      <c r="J41" s="32">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="35"/>
       <c r="B42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="17">
-        <v>44895</v>
-      </c>
-      <c r="D42" s="17">
-        <v>44862</v>
-      </c>
-      <c r="E42" s="17">
-        <v>44895</v>
-      </c>
-      <c r="F42" s="17">
-        <v>45072</v>
-      </c>
-      <c r="G42" s="17">
-        <v>44895</v>
-      </c>
-      <c r="H42" s="17">
-        <v>44862</v>
-      </c>
-      <c r="I42" s="17">
-        <v>44895</v>
-      </c>
-      <c r="J42" s="17">
-        <v>45072</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J42" s="31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="35"/>
       <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="H43" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I43" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="J43" s="31" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="C43" s="17">
+        <v>44895</v>
+      </c>
+      <c r="D43" s="17">
+        <v>44862</v>
+      </c>
+      <c r="E43" s="17">
+        <v>44895</v>
+      </c>
+      <c r="F43" s="17">
+        <v>45072</v>
+      </c>
+      <c r="G43" s="17">
+        <v>44895</v>
+      </c>
+      <c r="H43" s="17">
+        <v>44862</v>
+      </c>
+      <c r="I43" s="17">
+        <v>44895</v>
+      </c>
+      <c r="J43" s="17">
+        <v>45072</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="35"/>
       <c r="B44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F44" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="J44" s="31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" s="35"/>
+      <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C45" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D45" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="E45" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F44" s="31" t="s">
+      <c r="F45" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="G45" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="H44" s="16" t="s">
+      <c r="H45" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="I44" s="16" t="s">
+      <c r="I45" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="J44" s="31" t="s">
+      <c r="J45" s="31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="35"/>
-      <c r="B45" s="13" t="s">
+    <row r="46" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="35"/>
+      <c r="B46" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="23" t="s">
+      <c r="C46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="E45" s="23" t="s">
+      <c r="E46" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="F45" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="23" t="s">
+      <c r="F46" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="I45" s="23" t="s">
+      <c r="I46" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J45" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-      <c r="Q45" s="13"/>
-      <c r="R45" s="13"/>
-    </row>
-    <row r="49" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B50" s="9" t="s">
+      <c r="J46" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="13"/>
+      <c r="Q46" s="13"/>
+      <c r="R46" s="13"/>
+    </row>
+    <row r="50" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B51" s="4" t="s">
+      <c r="C51" s="19"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B52" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="6"/>
-    </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B52" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
@@ -5578,8 +5586,10 @@
       <c r="Q52" s="5"/>
       <c r="R52" s="6"/>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B53" s="4"/>
+    <row r="53" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B53" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -5597,31 +5607,50 @@
       <c r="Q53" s="5"/>
       <c r="R53" s="6"/>
     </row>
-    <row r="54" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="11"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-      <c r="O54" s="7"/>
-      <c r="P54" s="7"/>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="8"/>
+    <row r="54" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B54" s="4"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="6"/>
+    </row>
+    <row r="55" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="11"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7"/>
+      <c r="O55" s="7"/>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="A14:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5630,18 +5659,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B8B917-5635-4965-8A45-89E9AEAAEA05}">
-  <dimension ref="A1:O54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37" style="15" customWidth="1"/>
-    <col min="5" max="7" width="30.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="30.28515625" style="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37" style="15" customWidth="1"/>
-    <col min="9" max="10" width="30.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="30.28515625" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="B1" s="14" t="s">
         <v>53</v>
@@ -5676,7 +5705,7 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>54</v>
       </c>
@@ -5708,7 +5737,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="34"/>
       <c r="B3" t="s">
         <v>0</v>
@@ -5738,7 +5767,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="34"/>
       <c r="B4" t="s">
         <v>68</v>
@@ -5768,7 +5797,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="34"/>
       <c r="B5" t="s">
         <v>70</v>
@@ -5798,7 +5827,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="34"/>
       <c r="B6" t="s">
         <v>71</v>
@@ -5828,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="34"/>
       <c r="B7" t="s">
         <v>1</v>
@@ -5858,7 +5887,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="34"/>
       <c r="B8" t="s">
         <v>2</v>
@@ -5888,7 +5917,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="34"/>
       <c r="B9" t="s">
         <v>3</v>
@@ -5918,7 +5947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="34"/>
       <c r="B10" t="s">
         <v>4</v>
@@ -5948,7 +5977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="34"/>
       <c r="B11" t="s">
         <v>6</v>
@@ -5978,137 +6007,121 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="34"/>
-      <c r="B12" s="13" t="s">
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34"/>
+      <c r="B13" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C14" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D14" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>93</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G14" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H14" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I14" t="s">
         <v>93</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J14" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="18">
-        <v>8</v>
-      </c>
-      <c r="D14" s="16">
-        <v>61</v>
-      </c>
-      <c r="E14" s="16">
-        <v>53</v>
-      </c>
-      <c r="F14" s="16">
-        <v>8</v>
-      </c>
-      <c r="G14" s="18">
-        <v>8</v>
-      </c>
-      <c r="H14" s="16">
-        <v>61</v>
-      </c>
-      <c r="I14" s="16">
-        <v>53</v>
-      </c>
-      <c r="J14" s="16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="35"/>
       <c r="B15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="25">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="C15" s="18">
+        <v>8</v>
       </c>
       <c r="D15" s="16">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E15" s="16">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F15" s="16">
-        <v>0</v>
-      </c>
-      <c r="G15" s="25">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="G15" s="18">
+        <v>8</v>
       </c>
       <c r="H15" s="16">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I15" s="16">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J15" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="35"/>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="25">
         <v>0</v>
@@ -6135,317 +6148,317 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="35"/>
       <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="18">
+        <v>11</v>
+      </c>
+      <c r="C17" s="25">
         <v>0</v>
       </c>
       <c r="D17" s="16">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E17" s="16">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="F17" s="16">
-        <v>78</v>
-      </c>
-      <c r="G17" s="18">
+        <v>0</v>
+      </c>
+      <c r="G17" s="25">
         <v>0</v>
       </c>
       <c r="H17" s="16">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="I17" s="16">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="J17" s="16">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="35"/>
       <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="30">
-        <v>44013</v>
-      </c>
-      <c r="D18" s="17">
-        <v>44308</v>
-      </c>
-      <c r="E18" s="17">
-        <v>44448</v>
-      </c>
-      <c r="F18" s="17">
-        <v>44550</v>
-      </c>
-      <c r="G18" s="30">
-        <v>44013</v>
-      </c>
-      <c r="H18" s="17">
-        <v>44308</v>
-      </c>
-      <c r="I18" s="17">
-        <v>44448</v>
-      </c>
-      <c r="J18" s="17">
-        <v>44550</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="C18" s="18">
+        <v>0</v>
+      </c>
+      <c r="D18" s="16">
+        <v>95</v>
+      </c>
+      <c r="E18" s="16">
+        <v>97</v>
+      </c>
+      <c r="F18" s="16">
+        <v>78</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <v>95</v>
+      </c>
+      <c r="I18" s="16">
+        <v>97</v>
+      </c>
+      <c r="J18" s="16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="35"/>
       <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="C19" s="30">
+        <v>44013</v>
+      </c>
+      <c r="D19" s="17">
+        <v>44308</v>
+      </c>
+      <c r="E19" s="17">
+        <v>44448</v>
+      </c>
+      <c r="F19" s="17">
+        <v>44550</v>
+      </c>
+      <c r="G19" s="30">
+        <v>44013</v>
+      </c>
+      <c r="H19" s="17">
+        <v>44308</v>
+      </c>
+      <c r="I19" s="17">
+        <v>44448</v>
+      </c>
+      <c r="J19" s="17">
+        <v>44550</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="35"/>
       <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="30">
-        <v>44136</v>
-      </c>
-      <c r="D20" s="17">
-        <v>44386</v>
-      </c>
-      <c r="E20" s="17">
-        <v>44520</v>
-      </c>
-      <c r="F20" s="17">
-        <v>44614</v>
-      </c>
-      <c r="G20" s="30">
-        <v>44136</v>
-      </c>
-      <c r="H20" s="17">
-        <v>44386</v>
-      </c>
-      <c r="I20" s="17">
-        <v>44520</v>
-      </c>
-      <c r="J20" s="17">
-        <v>44614</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="35"/>
       <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C21" s="30">
+        <v>44136</v>
+      </c>
+      <c r="D21" s="17">
+        <v>44386</v>
+      </c>
+      <c r="E21" s="17">
+        <v>44520</v>
+      </c>
+      <c r="F21" s="17">
+        <v>44614</v>
+      </c>
+      <c r="G21" s="30">
+        <v>44136</v>
+      </c>
+      <c r="H21" s="17">
+        <v>44386</v>
+      </c>
+      <c r="I21" s="17">
+        <v>44520</v>
+      </c>
+      <c r="J21" s="17">
+        <v>44614</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="35"/>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="35"/>
       <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="35"/>
+      <c r="B24" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
+      <c r="C24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C25" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>93</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F25" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G25" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H25" t="s">
         <v>93</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I25" t="s">
         <v>97</v>
       </c>
-      <c r="J24" s="16" t="s">
+      <c r="J25" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="16">
-        <v>61</v>
-      </c>
-      <c r="D25" s="16">
-        <v>53</v>
-      </c>
-      <c r="E25" s="16">
-        <v>8</v>
-      </c>
-      <c r="F25" s="25">
-        <v>46</v>
-      </c>
-      <c r="G25" s="16">
-        <v>61</v>
-      </c>
-      <c r="H25" s="16">
-        <v>53</v>
-      </c>
-      <c r="I25" s="16">
-        <v>8</v>
-      </c>
-      <c r="J25" s="25">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="37"/>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C26" s="16">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D26" s="16">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="E26" s="16">
-        <v>0</v>
-      </c>
-      <c r="F26" s="16">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="F26" s="25">
+        <v>46</v>
       </c>
       <c r="G26" s="16">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H26" s="16">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I26" s="16">
-        <v>0</v>
-      </c>
-      <c r="J26" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="J26" s="25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="37"/>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27" s="16">
         <v>0</v>
@@ -6472,317 +6485,317 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="37"/>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28" s="16">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D28" s="16">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="E28" s="16">
-        <v>78</v>
-      </c>
-      <c r="F28" s="25">
-        <v>94</v>
+        <v>0</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0</v>
       </c>
       <c r="G28" s="16">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H28" s="16">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="I28" s="16">
-        <v>78</v>
-      </c>
-      <c r="J28" s="25">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="37"/>
       <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="17">
-        <v>44308</v>
-      </c>
-      <c r="D29" s="17">
-        <v>44448</v>
-      </c>
-      <c r="E29" s="17">
-        <v>44550</v>
-      </c>
-      <c r="F29" s="17">
-        <v>44693</v>
-      </c>
-      <c r="G29" s="17">
-        <v>44308</v>
-      </c>
-      <c r="H29" s="17">
-        <v>44448</v>
-      </c>
-      <c r="I29" s="17">
-        <v>44550</v>
-      </c>
-      <c r="J29" s="17">
-        <v>44693</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="C29" s="16">
+        <v>95</v>
+      </c>
+      <c r="D29" s="16">
+        <v>97</v>
+      </c>
+      <c r="E29" s="16">
+        <v>78</v>
+      </c>
+      <c r="F29" s="25">
+        <v>94</v>
+      </c>
+      <c r="G29" s="16">
+        <v>95</v>
+      </c>
+      <c r="H29" s="16">
+        <v>97</v>
+      </c>
+      <c r="I29" s="16">
+        <v>78</v>
+      </c>
+      <c r="J29" s="25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="37"/>
       <c r="B30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="C30" s="17">
+        <v>44308</v>
+      </c>
+      <c r="D30" s="17">
+        <v>44448</v>
+      </c>
+      <c r="E30" s="17">
+        <v>44550</v>
+      </c>
+      <c r="F30" s="17">
+        <v>44693</v>
+      </c>
+      <c r="G30" s="17">
+        <v>44308</v>
+      </c>
+      <c r="H30" s="17">
+        <v>44448</v>
+      </c>
+      <c r="I30" s="17">
+        <v>44550</v>
+      </c>
+      <c r="J30" s="17">
+        <v>44693</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="37"/>
       <c r="B31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="17">
-        <v>44386</v>
-      </c>
-      <c r="D31" s="17">
-        <v>44520</v>
-      </c>
-      <c r="E31" s="17">
-        <v>44614</v>
-      </c>
-      <c r="F31" s="17">
-        <v>44852</v>
-      </c>
-      <c r="G31" s="17">
-        <v>44386</v>
-      </c>
-      <c r="H31" s="17">
-        <v>44520</v>
-      </c>
-      <c r="I31" s="17">
-        <v>44614</v>
-      </c>
-      <c r="J31" s="17">
-        <v>44852</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="37"/>
       <c r="B32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="C32" s="17">
+        <v>44386</v>
+      </c>
+      <c r="D32" s="17">
+        <v>44520</v>
+      </c>
+      <c r="E32" s="17">
+        <v>44614</v>
+      </c>
+      <c r="F32" s="17">
+        <v>44852</v>
+      </c>
+      <c r="G32" s="17">
+        <v>44386</v>
+      </c>
+      <c r="H32" s="17">
+        <v>44520</v>
+      </c>
+      <c r="I32" s="17">
+        <v>44614</v>
+      </c>
+      <c r="J32" s="17">
+        <v>44852</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="37"/>
       <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C34" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E34" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F34" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G34" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H34" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I34" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="16" t="s">
+      <c r="J34" s="16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="38"/>
-      <c r="B34" s="13" t="s">
+    <row r="35" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="38"/>
+      <c r="B35" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="35" t="s">
+      <c r="C35" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>34</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>93</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E36" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F36" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G36" t="s">
         <v>93</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H36" t="s">
         <v>97</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I36" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J35" s="16" t="s">
+      <c r="J36" s="16" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="35"/>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="16">
-        <v>53</v>
-      </c>
-      <c r="D36" s="16">
-        <v>8</v>
-      </c>
-      <c r="E36" s="25">
-        <v>46</v>
-      </c>
-      <c r="F36" s="25">
-        <v>1.5</v>
-      </c>
-      <c r="G36" s="16">
-        <v>53</v>
-      </c>
-      <c r="H36" s="16">
-        <v>8</v>
-      </c>
-      <c r="I36" s="25">
-        <v>46</v>
-      </c>
-      <c r="J36" s="25">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="35"/>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C37" s="16">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D37" s="16">
-        <v>0</v>
-      </c>
-      <c r="E37" s="16">
-        <v>0</v>
-      </c>
-      <c r="F37" s="16">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="E37" s="25">
+        <v>46</v>
+      </c>
+      <c r="F37" s="25">
+        <v>1.5</v>
       </c>
       <c r="G37" s="16">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H37" s="16">
-        <v>0</v>
-      </c>
-      <c r="I37" s="16">
-        <v>0</v>
-      </c>
-      <c r="J37" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="I37" s="25">
+        <v>46</v>
+      </c>
+      <c r="J37" s="25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="35"/>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="16">
         <v>0</v>
@@ -6809,257 +6822,271 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="35"/>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39" s="16">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D39" s="16">
-        <v>78</v>
-      </c>
-      <c r="E39" s="25">
-        <v>94</v>
+        <v>0</v>
+      </c>
+      <c r="E39" s="16">
+        <v>0</v>
       </c>
       <c r="F39" s="16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G39" s="16">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H39" s="16">
-        <v>78</v>
-      </c>
-      <c r="I39" s="25">
-        <v>94</v>
+        <v>0</v>
+      </c>
+      <c r="I39" s="16">
+        <v>0</v>
       </c>
       <c r="J39" s="16">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="35"/>
       <c r="B40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="17">
-        <v>44448</v>
-      </c>
-      <c r="D40" s="17">
-        <v>44550</v>
-      </c>
-      <c r="E40" s="17">
-        <v>44693</v>
-      </c>
-      <c r="F40" s="17">
-        <v>45056</v>
-      </c>
-      <c r="G40" s="17">
-        <v>44448</v>
-      </c>
-      <c r="H40" s="17">
-        <v>44550</v>
-      </c>
-      <c r="I40" s="17">
-        <v>44693</v>
-      </c>
-      <c r="J40" s="17">
-        <v>45056</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="C40" s="16">
+        <v>97</v>
+      </c>
+      <c r="D40" s="16">
+        <v>78</v>
+      </c>
+      <c r="E40" s="25">
+        <v>94</v>
+      </c>
+      <c r="F40" s="16">
+        <v>14</v>
+      </c>
+      <c r="G40" s="16">
+        <v>97</v>
+      </c>
+      <c r="H40" s="16">
+        <v>78</v>
+      </c>
+      <c r="I40" s="25">
+        <v>94</v>
+      </c>
+      <c r="J40" s="16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="35"/>
       <c r="B41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H41" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="C41" s="17">
+        <v>44448</v>
+      </c>
+      <c r="D41" s="17">
+        <v>44550</v>
+      </c>
+      <c r="E41" s="17">
+        <v>44693</v>
+      </c>
+      <c r="F41" s="17">
+        <v>45056</v>
+      </c>
+      <c r="G41" s="17">
+        <v>44448</v>
+      </c>
+      <c r="H41" s="17">
+        <v>44550</v>
+      </c>
+      <c r="I41" s="17">
+        <v>44693</v>
+      </c>
+      <c r="J41" s="17">
+        <v>45056</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="35"/>
       <c r="B42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="17">
-        <v>44520</v>
-      </c>
-      <c r="D42" s="17">
-        <v>44614</v>
-      </c>
-      <c r="E42" s="17">
-        <v>44852</v>
-      </c>
-      <c r="F42" s="17">
-        <v>45072</v>
-      </c>
-      <c r="G42" s="17">
-        <v>44520</v>
-      </c>
-      <c r="H42" s="17">
-        <v>44614</v>
-      </c>
-      <c r="I42" s="17">
-        <v>44852</v>
-      </c>
-      <c r="J42" s="17">
-        <v>45072</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="35"/>
       <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="H43" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="J43" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="C43" s="17">
+        <v>44520</v>
+      </c>
+      <c r="D43" s="17">
+        <v>44614</v>
+      </c>
+      <c r="E43" s="17">
+        <v>44852</v>
+      </c>
+      <c r="F43" s="17">
+        <v>45072</v>
+      </c>
+      <c r="G43" s="17">
+        <v>44520</v>
+      </c>
+      <c r="H43" s="17">
+        <v>44614</v>
+      </c>
+      <c r="I43" s="17">
+        <v>44852</v>
+      </c>
+      <c r="J43" s="17">
+        <v>45072</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="35"/>
       <c r="B44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="35"/>
+      <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C45" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D45" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="E45" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="F45" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="G45" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H44" s="16" t="s">
+      <c r="H45" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="16" t="s">
+      <c r="I45" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="J44" s="16" t="s">
+      <c r="J45" s="16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="35"/>
-      <c r="B45" s="13" t="s">
+    <row r="46" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="35"/>
+      <c r="B46" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="13"/>
-    </row>
-    <row r="49" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B50" s="9" t="s">
+      <c r="C46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+    </row>
+    <row r="50" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B51" s="4"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="6"/>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C51" s="19"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B52" s="4"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
@@ -7075,7 +7102,7 @@
       <c r="N52" s="5"/>
       <c r="O52" s="6"/>
     </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B53" s="4"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
@@ -7091,28 +7118,44 @@
       <c r="N53" s="5"/>
       <c r="O53" s="6"/>
     </row>
-    <row r="54" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="11"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-      <c r="O54" s="8"/>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B54" s="4"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="6"/>
+    </row>
+    <row r="55" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="11"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7"/>
+      <c r="O55" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="A14:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
